--- a/tasks/finalpool/terminal-canvas-wc-excel-ppt-email/groundtruth_workspace/Student_Purchase_Analysis.xlsx
+++ b/tasks/finalpool/terminal-canvas-wc-excel-ppt-email/groundtruth_workspace/Student_Purchase_Analysis.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,26 +420,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Student_Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Student_ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Average_Score</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Submission_Count</t>
         </is>
@@ -444,14 +448,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Harry Taylor</t>
+          <t>Evan Parker</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>208</v>
+        <v>107</v>
       </c>
       <c r="C2" t="n">
-        <v>78.2</v>
+        <v>78</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
@@ -460,30 +464,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Evan Parker</t>
+          <t>Charlotte Bailey</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C3" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alice Campbell</t>
+          <t>Sophia White</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>399</v>
+        <v>115</v>
       </c>
       <c r="C4" t="n">
-        <v>60.6</v>
+        <v>71.8</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
@@ -492,30 +496,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Joseph Johnson</t>
+          <t>Nathan Cook</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>361</v>
+        <v>179</v>
       </c>
       <c r="C5" t="n">
-        <v>66.5</v>
+        <v>58.4</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Joseph Campbell</t>
+          <t>Andrew Moore</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>338</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>66.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -524,30 +528,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alice Evans</t>
+          <t>Sean Wright</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="C7" t="n">
-        <v>86.88</v>
+        <v>79.2</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sean Wright</t>
+          <t>Robert Baker</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C8" t="n">
-        <v>79.2</v>
+        <v>67.8</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
@@ -556,14 +560,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Thomas Morris</t>
+          <t>Harry Taylor</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>728</v>
+        <v>208</v>
       </c>
       <c r="C9" t="n">
-        <v>66</v>
+        <v>78.2</v>
       </c>
       <c r="D9" t="n">
         <v>5</v>
@@ -572,30 +576,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nathan Cook</t>
+          <t>Alice Evans</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>179</v>
+        <v>238</v>
       </c>
       <c r="C10" t="n">
-        <v>58.4</v>
+        <v>86.88</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Oscar Bailey</t>
+          <t>Isaac Thomas</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>785</v>
+        <v>263</v>
       </c>
       <c r="C11" t="n">
-        <v>64.8</v>
+        <v>67.8</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -604,30 +608,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Oscar Smith</t>
+          <t>Joseph Davis</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>565</v>
+        <v>330</v>
       </c>
       <c r="C12" t="n">
-        <v>85.2</v>
+        <v>77.5</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sophia White</t>
+          <t>Amy Davis</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>115</v>
+        <v>334</v>
       </c>
       <c r="C13" t="n">
-        <v>71.8</v>
+        <v>78.2</v>
       </c>
       <c r="D13" t="n">
         <v>5</v>
@@ -636,49 +640,113 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Charlotte Bailey</t>
+          <t>Joseph Campbell</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>113</v>
+        <v>338</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>66.2</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Andrew Moore</t>
+          <t>Joseph Johnson</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>185</v>
+        <v>361</v>
       </c>
       <c r="C15" t="n">
-        <v>71.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Joseph Davis</t>
+          <t>Alice Campbell</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>330</v>
+        <v>399</v>
       </c>
       <c r="C16" t="n">
-        <v>77.5</v>
+        <v>60.6</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sophie Rivera</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>473</v>
+      </c>
+      <c r="C17" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Oscar Smith</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>565</v>
+      </c>
+      <c r="C18" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Thomas Morris</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>728</v>
+      </c>
+      <c r="C19" t="n">
+        <v>66</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Oscar Bailey</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>785</v>
+      </c>
+      <c r="C20" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -692,31 +760,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Student_Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Bookstore_Customer_ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Total_Electronics_Spend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Electronics_Order_Count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Electronics_Item_Count</t>
         </is>
@@ -725,286 +793,362 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Harry Taylor</t>
+          <t>Evan Parker</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1163.15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
         <v>9</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3159.96</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Evan Parker</t>
+          <t>Charlotte Bailey</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C3" t="n">
-        <v>1163.15</v>
+        <v>18.66</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alice Campbell</t>
+          <t>Sophia White</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C4" t="n">
-        <v>2148.25</v>
+        <v>1068.51</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Joseph Johnson</t>
+          <t>Nathan Cook</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" t="n">
-        <v>84.33</v>
+        <v>36.12</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Joseph Campbell</t>
+          <t>Andrew Moore</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C6" t="n">
-        <v>3.62</v>
+        <v>62.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alice Evans</t>
+          <t>Sean Wright</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" t="n">
-        <v>359.29</v>
+        <v>485.28</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sean Wright</t>
+          <t>Robert Baker</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>485.28</v>
+        <v>75.84</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Thomas Morris</t>
+          <t>Harry Taylor</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>797.04</v>
+        <v>3159.96</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nathan Cook</t>
+          <t>Alice Evans</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>36.12</v>
+        <v>359.29</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Oscar Bailey</t>
+          <t>Isaac Thomas</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>780.29</v>
+        <v>107.74</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Oscar Smith</t>
+          <t>Joseph Davis</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>36.07</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sophia White</t>
+          <t>Amy Davis</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="C13" t="n">
-        <v>1068.51</v>
+        <v>24.08</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Charlotte Bailey</t>
+          <t>Joseph Campbell</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>18.66</v>
+        <v>3.62</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Andrew Moore</t>
+          <t>Joseph Johnson</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C15" t="n">
-        <v>62.5</v>
+        <v>84.33</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Joseph Davis</t>
+          <t>Alice Campbell</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C16" t="n">
-        <v>65.81999999999999</v>
+        <v>2148.25</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sophie Rivera</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>28</v>
+      </c>
+      <c r="C17" t="n">
+        <v>26.11</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Oscar Smith</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>25</v>
+      </c>
+      <c r="C18" t="n">
+        <v>36.07</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Thomas Morris</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>23</v>
+      </c>
+      <c r="C19" t="n">
+        <v>797.04</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Oscar Bailey</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>21</v>
+      </c>
+      <c r="C20" t="n">
+        <v>780.29</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1022,12 +1166,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -1040,7 +1184,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.0512</v>
       </c>
     </row>
     <row r="3">
@@ -1050,7 +1194,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8093</v>
+        <v>0.835</v>
       </c>
     </row>
     <row r="4">
@@ -1060,7 +1204,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72.78</v>
+        <v>72.56999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1070,7 +1214,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>684.59</v>
+        <v>552.77</v>
       </c>
     </row>
     <row r="6">
@@ -1080,7 +1224,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -1110,12 +1254,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Details</t>
         </is>
@@ -1141,7 +1285,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Target marketing campaigns toward students with average scores above 72.78 who show higher electronics purchasing potential</t>
+          <t>Target marketing campaigns toward students with average scores above 72.57 who show higher electronics purchasing potential</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1297,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stock electronics inventory based on 15 identified student purchasers with mean spending of $684.59</t>
+          <t>Stock electronics inventory based on 19 identified student purchasers with mean spending of $552.77</t>
         </is>
       </c>
     </row>
